--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-12).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-12).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-168</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R$ 1.647.578,14</t>
-  </si>
-  <si>
-    <t>R$ 9.003,16
-R$ 9.302,19</t>
-  </si>
-  <si>
-    <t>174.9%
-183.2%</t>
-  </si>
-  <si>
-    <t>98.1</t>
-  </si>
-  <si>
-    <t>153.1%</t>
+169</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 1.654.224,50</t>
+  </si>
+  <si>
+    <t>R$ 8.990,35
+R$ 9.286,47</t>
+  </si>
+  <si>
+    <t>174.4%
+182.7%</t>
+  </si>
+  <si>
+    <t>97.9</t>
+  </si>
+  <si>
+    <t>152.6%</t>
   </si>
   <si>
     <t>7.8%</t>
   </si>
   <si>
-    <t>(37.7%)</t>
+    <t>(37.6%)</t>
   </si>
   <si>
     <t>2.4%</t>
@@ -956,13 +956,13 @@
     <t>53.3%</t>
   </si>
   <si>
-    <t>22.6%</t>
+    <t>22.5%</t>
   </si>
   <si>
     <t>8.3</t>
   </si>
   <si>
-    <t>9.9</t>
+    <t>9.8</t>
   </si>
   <si>
     <t>18.1</t>
@@ -971,10 +971,10 @@
     <t>24.5</t>
   </si>
   <si>
-    <t>54.7%</t>
-  </si>
-  <si>
-    <t>-R$ 42.366,89</t>
+    <t>54.6%</t>
+  </si>
+  <si>
+    <t>-R$ 42.418,79</t>
   </si>
   <si>
     <t>2.94</t>
@@ -11071,7 +11071,7 @@
         <v>-777.29999999999995</v>
       </c>
       <c r="AH76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="11"/>
       <c r="AJ76" s="13">
@@ -16511,7 +16511,7 @@
         <v>-76.900000000000006</v>
       </c>
       <c r="AH120" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13">
@@ -19172,10 +19172,10 @@
         <v>2.1052631578947367</v>
       </c>
       <c r="T141" s="6">
-        <v>0.32843574260976272</v>
+        <v>0.15661233720334888</v>
       </c>
       <c r="U141" s="6">
-        <v>0.015374906462532156</v>
+        <v>-0.15644849894388166</v>
       </c>
       <c r="V141" s="6">
         <v>0.096404326457681669</v>
@@ -21370,7 +21370,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>44</v>
@@ -21406,27 +21406,61 @@
       <c t="s" r="N159" s="4">
         <v>52</v>
       </c>
-      <c r="O159" s="5"/>
-      <c r="P159" s="5"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="7"/>
-      <c r="S159" s="6"/>
-      <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6"/>
-      <c r="X159" s="8"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="6"/>
-      <c r="AA159" s="8"/>
-      <c r="AB159" s="8"/>
+      <c r="O159" s="5">
+        <v>6646.3599999999997</v>
+      </c>
+      <c r="P159" s="5">
+        <v>6646.3599999999997</v>
+      </c>
+      <c r="Q159" s="6">
+        <v>0.89887319436825752</v>
+      </c>
+      <c r="R159" s="7">
+        <v>70</v>
+      </c>
+      <c r="S159" s="6">
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="T159" s="6">
+        <v>0.28319838227240174</v>
+      </c>
+      <c r="U159" s="6">
+        <v>-0.016364085002918891</v>
+      </c>
+      <c r="V159" s="6">
+        <v>0.033351413405232344</v>
+      </c>
+      <c r="W159" s="6">
+        <v>0.0011638701484722464</v>
+      </c>
+      <c r="X159" s="8">
+        <v>31.753268627450979</v>
+      </c>
+      <c r="Y159" s="6">
+        <v>0.60784313725490191</v>
+      </c>
+      <c r="Z159" s="6">
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="AA159" s="8">
+        <v>4.8057142857142852</v>
+      </c>
+      <c r="AB159" s="8">
+        <v>4.9892156862745098</v>
+      </c>
       <c r="AC159" s="8">
         <v>10.271894</v>
       </c>
-      <c r="AD159" s="8"/>
-      <c r="AE159" s="6"/>
+      <c r="AD159" s="8">
+        <v>17.210456862745097</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>0.47058823529411764</v>
+      </c>
       <c r="AF159" s="9"/>
-      <c r="AG159" s="5"/>
+      <c r="AG159" s="5">
+        <v>-51.899999999999999</v>
+      </c>
       <c r="AH159" s="10">
         <v>2</v>
       </c>
@@ -22651,7 +22685,7 @@
         <v>0.020491775861924789</v>
       </c>
       <c r="W169" s="6">
-        <v>-0.020788630871248544</v>
+        <v>-0.0097924523568615317</v>
       </c>
       <c r="X169" s="8">
         <v>29.080333999999997</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-12).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-12).xlsx
@@ -915,27 +915,27 @@
   </si>
   <si>
     <t>215
-169</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 1.654.224,50</t>
-  </si>
-  <si>
-    <t>R$ 8.990,35
-R$ 9.286,47</t>
+170</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 1.661.434,28</t>
+  </si>
+  <si>
+    <t>R$ 8.980,73
+R$ 9.274,26</t>
   </si>
   <si>
     <t>174.4%
 182.7%</t>
   </si>
   <si>
-    <t>97.9</t>
-  </si>
-  <si>
-    <t>152.6%</t>
+    <t>97.8</t>
+  </si>
+  <si>
+    <t>152.9%</t>
   </si>
   <si>
     <t>7.8%</t>
@@ -950,31 +950,31 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>33.3</t>
-  </si>
-  <si>
-    <t>53.3%</t>
-  </si>
-  <si>
-    <t>22.5%</t>
+    <t>33.6</t>
+  </si>
+  <si>
+    <t>53.1%</t>
+  </si>
+  <si>
+    <t>22.9%</t>
   </si>
   <si>
     <t>8.3</t>
   </si>
   <si>
-    <t>9.8</t>
+    <t>10.1</t>
   </si>
   <si>
     <t>18.1</t>
   </si>
   <si>
-    <t>24.5</t>
-  </si>
-  <si>
-    <t>54.6%</t>
-  </si>
-  <si>
-    <t>-R$ 42.418,79</t>
+    <t>24.8</t>
+  </si>
+  <si>
+    <t>54.4%</t>
+  </si>
+  <si>
+    <t>-R$ 42.505,49</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2216,10 +2216,10 @@
         <v>1.5283018867924527</v>
       </c>
       <c r="T7" s="6">
-        <v>0.3690859571057834</v>
+        <v>0.36818761703268049</v>
       </c>
       <c r="U7" s="6">
-        <v>-0.10534044897739016</v>
+        <v>-0.10623878905049305</v>
       </c>
       <c r="V7" s="6">
         <v>0.023836351602775134</v>
@@ -14255,7 +14255,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14291,25 +14291,59 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
+      <c r="O102" s="5">
+        <v>7209.7799999999997</v>
+      </c>
+      <c r="P102" s="5">
+        <v>7209.7799999999997</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>1.8660507715914423</v>
+      </c>
+      <c r="R102" s="7">
+        <v>74</v>
+      </c>
+      <c r="S102" s="6">
+        <v>2.2173913043478262</v>
+      </c>
+      <c r="T102" s="6">
+        <v>0.00031494719672444933</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.35523820421704966</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.0095260188244301481</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.0043523519441647316</v>
+      </c>
+      <c r="X102" s="8">
+        <v>117.15673829787234</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.1276595744680851</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>13.509685135135134</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>80.575363043478262</v>
+      </c>
       <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="AD102" s="8">
+        <v>99.531482222222223</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>-86.700000000000003</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-12).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-12).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-170</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 1.661.434,28</t>
-  </si>
-  <si>
-    <t>R$ 8.980,73
-R$ 9.274,26</t>
-  </si>
-  <si>
-    <t>174.4%
-182.7%</t>
+171</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.671.338,53</t>
+  </si>
+  <si>
+    <t>R$ 8.985,69
+R$ 9.277,94</t>
+  </si>
+  <si>
+    <t>174.1%
+182.3%</t>
   </si>
   <si>
     <t>97.8</t>
   </si>
   <si>
-    <t>152.9%</t>
-  </si>
-  <si>
-    <t>7.8%</t>
-  </si>
-  <si>
-    <t>(37.6%)</t>
+    <t>152.7%</t>
+  </si>
+  <si>
+    <t>7.7%</t>
+  </si>
+  <si>
+    <t>(37.5%)</t>
   </si>
   <si>
     <t>2.4%</t>
@@ -956,22 +956,22 @@
     <t>53.1%</t>
   </si>
   <si>
-    <t>22.9%</t>
+    <t>23.0%</t>
   </si>
   <si>
     <t>8.3</t>
   </si>
   <si>
-    <t>10.1</t>
-  </si>
-  <si>
-    <t>18.1</t>
+    <t>10.2</t>
+  </si>
+  <si>
+    <t>18.4</t>
   </si>
   <si>
     <t>24.8</t>
   </si>
   <si>
-    <t>54.4%</t>
+    <t>54.3%</t>
   </si>
   <si>
     <t>-R$ 42.505,49</t>
@@ -3924,7 +3924,7 @@
         <v>0.021824424575064769</v>
       </c>
       <c r="W20" s="6">
-        <v>0.00188624700404518</v>
+        <v>0.0020448011000373835</v>
       </c>
       <c r="X20" s="8">
         <v>28.114629999999998</v>
@@ -4836,7 +4836,7 @@
         <v>-1086.5</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -12634,7 +12634,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12668,25 +12668,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>9904.25</v>
+      </c>
+      <c r="P89" s="5">
+        <v>9904.25</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>1.2763733397075079</v>
+      </c>
+      <c r="R89" s="7">
+        <v>88</v>
+      </c>
+      <c r="S89" s="6">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-0.0002553449276825605</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.32167089885655148</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.016698336572683443</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0041592750586869273</v>
+      </c>
+      <c r="X89" s="8">
+        <v>36.33949347826087</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.39130434782608697</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.45652173913043476</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>6.3304032967032962</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>14.632935714285715</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>27.465580434782609</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.19565217391304349</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14216,7 +14250,7 @@
         <v>0</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -14333,7 +14367,9 @@
       <c r="AB102" s="8">
         <v>80.575363043478262</v>
       </c>
-      <c r="AC102" s="8"/>
+      <c r="AC102" s="8">
+        <v>94.276403000000002</v>
+      </c>
       <c r="AD102" s="8">
         <v>99.531482222222223</v>
       </c>
@@ -20132,7 +20168,7 @@
         <v>0.027852522162221935</v>
       </c>
       <c r="W148" s="6">
-        <v>-0.0020652369617518256</v>
+        <v>0.0077211579220462538</v>
       </c>
       <c r="X148" s="8">
         <v>36.245115517241381</v>
@@ -24744,7 +24780,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25691,7 +25727,7 @@
         <v>-93.799999999999997</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -26998,7 +27034,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>
@@ -27279,7 +27315,7 @@
         <v>0.072255653242697504</v>
       </c>
       <c r="W205" s="6">
-        <v>0.045506377535023138</v>
+        <v>0.044047759396987449</v>
       </c>
       <c r="X205" s="8">
         <v>51.885553333333334</v>
@@ -28407,7 +28443,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-12).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-12).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-171</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 1.671.338,53</t>
-  </si>
-  <si>
-    <t>R$ 8.985,69
-R$ 9.277,94</t>
-  </si>
-  <si>
-    <t>174.1%
-182.3%</t>
-  </si>
-  <si>
-    <t>97.8</t>
-  </si>
-  <si>
-    <t>152.7%</t>
-  </si>
-  <si>
-    <t>7.7%</t>
-  </si>
-  <si>
-    <t>(37.5%)</t>
+177</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 1.707.459,96</t>
+  </si>
+  <si>
+    <t>R$ 8.893,02
+R$ 9.167,51</t>
+  </si>
+  <si>
+    <t>173.6%
+181.4%</t>
+  </si>
+  <si>
+    <t>96.8</t>
+  </si>
+  <si>
+    <t>152.3%</t>
+  </si>
+  <si>
+    <t>8.2%</t>
+  </si>
+  <si>
+    <t>(36.8%)</t>
   </si>
   <si>
     <t>2.4%</t>
@@ -953,19 +953,19 @@
     <t>33.6</t>
   </si>
   <si>
-    <t>53.1%</t>
+    <t>53.5%</t>
   </si>
   <si>
     <t>23.0%</t>
   </si>
   <si>
-    <t>8.3</t>
-  </si>
-  <si>
-    <t>10.2</t>
-  </si>
-  <si>
-    <t>18.4</t>
+    <t>8.4</t>
+  </si>
+  <si>
+    <t>10.0</t>
+  </si>
+  <si>
+    <t>18.3</t>
   </si>
   <si>
     <t>24.8</t>
@@ -974,7 +974,7 @@
     <t>54.3%</t>
   </si>
   <si>
-    <t>-R$ 42.505,49</t>
+    <t>-R$ 42.750,87</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2069,7 +2069,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2105,25 +2105,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>13093.129999999999</v>
+      </c>
+      <c r="P6" s="5">
+        <v>13093.129999999999</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>2.8194438772235864</v>
+      </c>
+      <c r="R6" s="7">
+        <v>143</v>
+      </c>
+      <c r="S6" s="6">
+        <v>2.4878048780487805</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.27017805520910587</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.010428644640357195</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.016301296939692803</v>
+      </c>
+      <c r="W6" s="6">
+        <v>-0.0043736677173448982</v>
+      </c>
+      <c r="X6" s="8">
+        <v>38.975783760683761</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0.49572649572649574</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>21.028873239436621</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>3.7840452991452991</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>25.794301000000001</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>32.749429914529912</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.35897435897435898</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>-116.90000000000001</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -7880,7 +7916,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7916,25 +7952,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>1063.2</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1063.2</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>1.1140539250775472</v>
+      </c>
+      <c r="R51" s="7">
+        <v>11</v>
+      </c>
+      <c r="S51" s="6">
+        <v>1.2000000000000002</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.38340857787810378</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.043823363431151244</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.076577313769751687</v>
+      </c>
+      <c r="X51" s="8">
+        <v>23.11666</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>5.0791666666666666</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>28.25</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>21.119999999999997</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8807,7 +8877,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>10.388177000000001</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -20500,7 +20572,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20536,25 +20608,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>5111.71</v>
+      </c>
+      <c r="P151" s="5">
+        <v>5111.71</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>1.8533606479594971</v>
+      </c>
+      <c r="R151" s="7">
+        <v>59</v>
+      </c>
+      <c r="S151" s="6">
+        <v>1.8095238095238093</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.33739517695643922</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.007473761226673657</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.048792967519675413</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.021774611627028918</v>
+      </c>
+      <c r="X151" s="8">
+        <v>24.06180625</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>4.971311475409836</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>2.9482645833333332</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>7.4703710000000001</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>14.46180625</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.875</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>0</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21250,7 +21358,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21286,25 +21394,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>5914.7600000000002</v>
+      </c>
+      <c r="P157" s="5">
+        <v>5914.7600000000002</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>1.557966345051875</v>
+      </c>
+      <c r="R157" s="7">
+        <v>65</v>
+      </c>
+      <c r="S157" s="6">
+        <v>1.3214285714285716</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.2982119815512379</v>
+      </c>
+      <c r="U157" s="6">
+        <v>-0.01244982044918137</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.0437817426235384</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.023956762404560791</v>
+      </c>
+      <c r="X157" s="8">
+        <v>30.034375000000001</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0.0625</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>8.8478499999999993</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>3.9541666666666671</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>12.733679</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>19.677777083333336</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.54166666666666663</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>-176.80000000000001</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21345,7 +21489,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21381,25 +21525,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>4880.6999999999998</v>
+      </c>
+      <c r="P158" s="5">
+        <v>4880.6999999999998</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>1.1320176128322066</v>
+      </c>
+      <c r="R158" s="7">
+        <v>52</v>
+      </c>
+      <c r="S158" s="6">
+        <v>1.1666666666666665</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.26204831274202472</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.030274509803921566</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.029710389903087671</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.014316081709590839</v>
+      </c>
+      <c r="X158" s="8">
+        <v>33.026667500000002</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>7.1993716981132083</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>6.4733324999999997</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>13.721745</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>20.503332499999999</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.5</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>28.219999999999999</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22206,7 +22386,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22242,25 +22422,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>6057.9300000000003</v>
+      </c>
+      <c r="P165" s="5">
+        <v>6057.9300000000003</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>0.42006254160845402</v>
+      </c>
+      <c r="R165" s="7">
+        <v>70</v>
+      </c>
+      <c r="S165" s="6">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.28542838890512101</v>
+      </c>
+      <c r="U165" s="6">
+        <v>-0.0011051299701383146</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.027103565079160702</v>
+      </c>
+      <c r="W165" s="6">
+        <v>0.0016856417951346414</v>
+      </c>
+      <c r="X165" s="8">
+        <v>24.02282608695652</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.69565217391304346</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0.021739130434782608</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>5.9065217391304348</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>4.5906512195121953</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>10.812751</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>16.930434782608696</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0.84782608695652173</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>20.100000000000001</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
